--- a/IngSoftware/propuesta/CasosDeTests/Casos de Test - Alta - Gestionar Producto.xlsx
+++ b/IngSoftware/propuesta/CasosDeTests/Casos de Test - Alta - Gestionar Producto.xlsx
@@ -8,12 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\source\TrabajoFinalAus\IngSoftware\propuesta\CasosDeTests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C8E2420-0028-4EB2-B4ED-25B9614AAFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF2D743-ECC8-4765-9F27-947EDE1AB729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{907B4683-9A02-4D8C-B9E2-85A5E705A97A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{907B4683-9A02-4D8C-B9E2-85A5E705A97A}"/>
   </bookViews>
   <sheets>
     <sheet name="1A-ALTA" sheetId="1" r:id="rId1"/>
+    <sheet name="1B-ALTA, SIN CATEGORIAS" sheetId="2" r:id="rId2"/>
+    <sheet name="1C-ALTA, SIN UNIDADES" sheetId="4" r:id="rId3"/>
+    <sheet name="1E-ALTA NOMBRE MINIMO" sheetId="7" r:id="rId4"/>
+    <sheet name="1F-ALTA NOMBRE MAXIMO" sheetId="9" r:id="rId5"/>
+    <sheet name="1G-ALTA DESCRIPCION MAXIMA" sheetId="11" r:id="rId6"/>
+    <sheet name="1H-ALTA DESCRIPCION MINIMA" sheetId="12" r:id="rId7"/>
+    <sheet name="1I-ALTA CANTIDAD NEGATIVA" sheetId="13" r:id="rId8"/>
+    <sheet name="1J-ALTA CANTIDAD MAL FORMATO" sheetId="16" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="89">
   <si>
     <t>El Sistema muestra la grilla de Productos actualizada.</t>
   </si>
@@ -50,15 +58,9 @@
     <t>El usuario acepta el aviso.</t>
   </si>
   <si>
-    <t>El Sistema muestra un aviso indicando que el producto fue dado de alta exitosamente y con un boton que indica 'Aceptar'.</t>
-  </si>
-  <si>
     <t>Se selecciona la opcion de 'Guardar'.</t>
   </si>
   <si>
-    <t>El Sistema despliega una lista de Unidades que filtra mediante Nombre de Unidad, una vez que se selecciona, se esconde el listado.</t>
-  </si>
-  <si>
     <t>"Unidad"</t>
   </si>
   <si>
@@ -69,10 +71,6 @@
   </si>
   <si>
     <t>"Torta"</t>
-  </si>
-  <si>
-    <t>Se se selecciona la opción de Categoría, se despliega un listado de todas las categorias.
-Se utiliza el filtro de Nombre y se selecciona la Categoría.</t>
   </si>
   <si>
     <t>El Sistema indica visualmente que se seleccionó el campo de Tratar Unidad como Entero.</t>
@@ -145,16 +143,9 @@
     <t>Pasos de Ejecución</t>
   </si>
   <si>
-    <t>El Producto se da de alta</t>
-  </si>
-  <si>
     <t>Garantias de exito</t>
   </si>
   <si>
-    <t>* Existe al menos una Categoría "Torta" 
-* Existe al menos Unidad "Unidad" dada de alta</t>
-  </si>
-  <si>
     <t>Prerequisitos</t>
   </si>
   <si>
@@ -180,6 +171,176 @@
   </si>
   <si>
     <t xml:space="preserve">MISSTORTAS </t>
+  </si>
+  <si>
+    <t>No se produce el alta.</t>
+  </si>
+  <si>
+    <t>Alta Producto, sin categorias finales habilitadas.</t>
+  </si>
+  <si>
+    <t>* Existe al menos una Categoría final habilitada, con nombre "Torta" .
+* Existe al menos Unidad "Unidad" dada de alta.</t>
+  </si>
+  <si>
+    <t>El Producto se da de alta.</t>
+  </si>
+  <si>
+    <t>Se selecciona la opción de Categoría, se despliega un listado vacio de categorias.</t>
+  </si>
+  <si>
+    <t>Se selecciona la opción de Categoría, se despliega un listado de todas las categorias.
+Se utiliza el filtro de Nombre y se selecciona la Categoría.</t>
+  </si>
+  <si>
+    <t>Se selecciona el botón 'Agregar Producto'.</t>
+  </si>
+  <si>
+    <t>Se despliega la opción de Unidad, se utiliza el filtro y se selecciona la Unidad.</t>
+  </si>
+  <si>
+    <t>El Sistema despliega una lista vacia de Categorías.</t>
+  </si>
+  <si>
+    <t>El Sistema despliega una lista vacia de Categorías. Que se esconde al seleccionar otra opcion.</t>
+  </si>
+  <si>
+    <t>* NO existen Categorias finales habilitadas dadas de alta.
+* Existe al menos una Unidad dada de alta, con nombre "Unidad".</t>
+  </si>
+  <si>
+    <t>Se despliega la opción de Unidad, se utiliza el filtro.</t>
+  </si>
+  <si>
+    <t>El Sistema muestra el formulario de Alta de Producto con los siguientes campos:
+- Nombre.
+- Descripción.
+- Cantidad.
+- Tratar Unidad Como Entero.
+- Categoría.
+- Unidad
+Y una leyenda indicando que se está realizando el Alta de un Producto.
+El boton de Guardar figura deshabilitado, debido a que no existen Categorias finales habilitadas. El Sistema indica que no se puede guardar el formulario por esta razon.</t>
+  </si>
+  <si>
+    <t>Se selecciona la Descripción del Producto y se ingresa la entrada.</t>
+  </si>
+  <si>
+    <t>Se selecciona el Nombre del Producto y NO se ingresa  entrada.</t>
+  </si>
+  <si>
+    <t>El Sistema indica visualmente que se seleccionó el campo de Nombre pero deshabilita el boton de guardado con una leyenda que indica 'El Nombre de Producto debe tener mas de x caracteres y menos de y caracteres'.</t>
+  </si>
+  <si>
+    <t>1B</t>
+  </si>
+  <si>
+    <t>1C</t>
+  </si>
+  <si>
+    <t>Alta Producto, sin unidades habilitadas.</t>
+  </si>
+  <si>
+    <t>Cadena con largo menor a 'x'</t>
+  </si>
+  <si>
+    <t>Alta Producto, con largo de Nombre menor al esperado.</t>
+  </si>
+  <si>
+    <t>No se produce ninguna accion.</t>
+  </si>
+  <si>
+    <t>Cadena con largo mayor a 'y'</t>
+  </si>
+  <si>
+    <t>Alta Producto, con largo de Nombre mayor al esperado.</t>
+  </si>
+  <si>
+    <t>1E</t>
+  </si>
+  <si>
+    <t>1F</t>
+  </si>
+  <si>
+    <t>Se selecciona el Nombre del Producto y se ingresa  la entrada.</t>
+  </si>
+  <si>
+    <t>1G</t>
+  </si>
+  <si>
+    <t>Entrada con largo mayor a 'y'.</t>
+  </si>
+  <si>
+    <t>El Sistema indica visualmente que se seleccionó el campo de Descripcion pero deshabilita el boton de guardado con una leyenda que indica 'La Descripcion del Producto debe tener mas de x caracteres y menos de y caracteres'.</t>
+  </si>
+  <si>
+    <t>No se produce ninguna accion. El Sistema permite unicamente modificar los datos del formulario y cancelar el mismo.</t>
+  </si>
+  <si>
+    <t>Entrada con largo menor a 'x'.</t>
+  </si>
+  <si>
+    <t>1H</t>
+  </si>
+  <si>
+    <t>Alta Producto, con largo de Descripcion menor a la esperada.</t>
+  </si>
+  <si>
+    <t>Alta Producto, con largo de Descripcion mayor al esperada.</t>
+  </si>
+  <si>
+    <t>"-5"</t>
+  </si>
+  <si>
+    <t>El Sistema indica visualmente que se seleccionó el campo de Cantidad y toma la entrada.</t>
+  </si>
+  <si>
+    <t>El Sistema indica visualmente que se seleccionó el campo de Cantidad y toma la entrada.
+El Sistema deshabilita la opcion de Guardar indicando que la cantidad ingresada es negativa.</t>
+  </si>
+  <si>
+    <t>1I</t>
+  </si>
+  <si>
+    <t>Alta Producto, la cantidad es negativa</t>
+  </si>
+  <si>
+    <t>"5.5"</t>
+  </si>
+  <si>
+    <t>El Sistema indica que si la unidad es tratada como entero, la cantidad debe ser un valor entero positivo.</t>
+  </si>
+  <si>
+    <t>El Administrador de Producto acepta el aviso.</t>
+  </si>
+  <si>
+    <t>El Sistema indica que si la unidad es tratada como entero, la cantidad debe ser un valor entero positivo.  El Sistema permite unicamente modificar los datos del formulario y cancelar el mismo.</t>
+  </si>
+  <si>
+    <t>Alta Producto, la cantidad no tiene el formato correcto.</t>
+  </si>
+  <si>
+    <t>El Sistema muestra un aviso indicando que el producto fue dado de alta exitosamente.</t>
+  </si>
+  <si>
+    <t>El Sistema despliega una lista de Unidades que filtra mediante Nombre de Unidad y selecciona la Unidad. El listado desaparece.</t>
+  </si>
+  <si>
+    <t>Se selecciona la opción de Categoría.</t>
+  </si>
+  <si>
+    <t>El Sistema muestra el formulario de Alta de Producto con los siguientes campos:
+- Nombre.
+- Descripción.
+- Cantidad.
+- Tratar Unidad Como Entero.
+- Categoría.
+- Unidad
+Y una leyenda indicando que se está realizando el Alta de un Producto.
+El boton de Guardar queda deshabilitado, debido a que no existen Categorias finales habilitadas. El Sistema indica que no se puede guardar el formulario por esta razon.</t>
+  </si>
+  <si>
+    <t>1J</t>
   </si>
 </sst>
 </file>
@@ -384,7 +545,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -406,23 +566,44 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -430,44 +611,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="108">
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -600,35 +763,1435 @@
     <dxf>
       <border outline="0">
         <top style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -657,16 +2220,144 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6E43AC89-0E5C-4246-B8B3-33610FC8FE6B}" name="Table2" displayName="Table2" ref="A7:G19" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
-  <autoFilter ref="A7:G19" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6E43AC89-0E5C-4246-B8B3-33610FC8FE6B}" name="Table2" displayName="Table2" ref="A7:G17" totalsRowShown="0" headerRowDxfId="107" dataDxfId="105" headerRowBorderDxfId="106" tableBorderDxfId="104" totalsRowBorderDxfId="103">
+  <autoFilter ref="A7:G17" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{24A6AD19-968B-4D0F-B19E-91A01420FF78}" name="Numero de Paso" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{D4259866-411E-40F1-898D-D467FD215EC2}" name="Accion" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{FBAC7A91-627A-4C9B-BD4C-A3B94C9780B5}" name="Entrada" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{AE9E749A-B854-4DB6-92F6-C0859F6DABD9}" name="Salida Esperada" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{0B1663DB-C235-4B08-86E1-8189BABE6031}" name="Salida Actual" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{CE6EDC0F-1D3F-474B-947A-9682A43024E4}" name="Resultados" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{2D5B2493-59B7-45F1-AE14-8D2B13987E17}" name="Comentarios" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{24A6AD19-968B-4D0F-B19E-91A01420FF78}" name="Numero de Paso" dataDxfId="102"/>
+    <tableColumn id="2" xr3:uid="{D4259866-411E-40F1-898D-D467FD215EC2}" name="Accion" dataDxfId="101"/>
+    <tableColumn id="3" xr3:uid="{FBAC7A91-627A-4C9B-BD4C-A3B94C9780B5}" name="Entrada" dataDxfId="100"/>
+    <tableColumn id="4" xr3:uid="{AE9E749A-B854-4DB6-92F6-C0859F6DABD9}" name="Salida Esperada" dataDxfId="99"/>
+    <tableColumn id="5" xr3:uid="{0B1663DB-C235-4B08-86E1-8189BABE6031}" name="Salida Actual" dataDxfId="98"/>
+    <tableColumn id="6" xr3:uid="{CE6EDC0F-1D3F-474B-947A-9682A43024E4}" name="Resultados" dataDxfId="97"/>
+    <tableColumn id="7" xr3:uid="{2D5B2493-59B7-45F1-AE14-8D2B13987E17}" name="Comentarios" dataDxfId="96"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7B53F065-0A42-4440-AB05-93E7117A02CE}" name="Table23" displayName="Table23" ref="A7:G16" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94" headerRowBorderDxfId="92" tableBorderDxfId="93" totalsRowBorderDxfId="91">
+  <autoFilter ref="A7:G16" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{6BA9AEE1-7B18-48DF-873D-5B752A4414A2}" name="Numero de Paso" dataDxfId="90"/>
+    <tableColumn id="2" xr3:uid="{5666DADB-B020-4932-BD8A-195D02BDE5BB}" name="Accion" dataDxfId="89"/>
+    <tableColumn id="3" xr3:uid="{C3825420-E883-4CAD-88B8-3E485C202466}" name="Entrada" dataDxfId="88"/>
+    <tableColumn id="4" xr3:uid="{E4FDF7F0-E2D7-4804-B435-9123CCB5F893}" name="Salida Esperada" dataDxfId="87"/>
+    <tableColumn id="5" xr3:uid="{8FA2866F-A888-4C75-A9A7-CB0B6CC84E2B}" name="Salida Actual" dataDxfId="86"/>
+    <tableColumn id="6" xr3:uid="{4FBEAAE0-81E3-414A-9EAB-B51CDAF1C6F4}" name="Resultados" dataDxfId="85"/>
+    <tableColumn id="7" xr3:uid="{C56913EB-9B3A-4C86-8B80-1427712DC5F8}" name="Comentarios" dataDxfId="84"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0D309353-38F3-4507-B6CE-579B4A0BFC4B}" name="Table234" displayName="Table234" ref="A7:G16" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82" headerRowBorderDxfId="80" tableBorderDxfId="81" totalsRowBorderDxfId="79">
+  <autoFilter ref="A7:G16" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{01239695-3B48-4A9A-B581-8CC775C80CEC}" name="Numero de Paso" dataDxfId="78"/>
+    <tableColumn id="2" xr3:uid="{C2BB6267-B9E6-49F2-A345-7534F986316A}" name="Accion" dataDxfId="77"/>
+    <tableColumn id="3" xr3:uid="{52A9CB81-E8AB-46ED-966D-80625129ED7A}" name="Entrada" dataDxfId="76"/>
+    <tableColumn id="4" xr3:uid="{D5EC15BE-F878-4459-AE71-852327D1FB60}" name="Salida Esperada" dataDxfId="75"/>
+    <tableColumn id="5" xr3:uid="{1F451792-AE2A-4151-8225-E9EB524DB7F0}" name="Salida Actual" dataDxfId="74"/>
+    <tableColumn id="6" xr3:uid="{DD1DE444-F7DB-4F81-8D8E-97394DFA33DD}" name="Resultados" dataDxfId="73"/>
+    <tableColumn id="7" xr3:uid="{FEE8DEA1-5C76-451F-87FF-FE3C18A46FE0}" name="Comentarios" dataDxfId="72"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{88896973-A502-4B2D-A400-F2EBC876E98B}" name="Table256" displayName="Table256" ref="A7:G16" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46" headerRowBorderDxfId="44" tableBorderDxfId="45" totalsRowBorderDxfId="43">
+  <autoFilter ref="A7:G16" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{DC62C5B6-2C91-480B-A174-7BA14D1BE90B}" name="Numero de Paso" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{E12C0F11-9B9B-49BE-9832-1C73732FAC99}" name="Accion" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{92184EAD-66A2-4D37-A4AF-2FA0F5195F3C}" name="Entrada" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{78BE0E53-20FD-45D7-97ED-02A26094AD96}" name="Salida Esperada" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{12F1E81D-CDFD-45AB-ABB3-061E27D4C11B}" name="Salida Actual" dataDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{A9BDC0DB-3985-4EB3-AB0A-7FFD97A3EA03}" name="Resultados" dataDxfId="37"/>
+    <tableColumn id="7" xr3:uid="{0F9C5F13-991F-4604-89D8-C2E11ADCE109}" name="Comentarios" dataDxfId="36"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{077CEA3D-AAB9-43A6-B0DC-00F3AAD2FDE5}" name="Table2567" displayName="Table2567" ref="A7:G16" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70" headerRowBorderDxfId="68" tableBorderDxfId="69" totalsRowBorderDxfId="67">
+  <autoFilter ref="A7:G16" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{E9EBABE0-38F7-4882-8510-9F459E48840B}" name="Numero de Paso" dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{0A480DAF-1808-4DA9-8DEA-A389417A5487}" name="Accion" dataDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{62853D11-8CAC-4351-B350-7BB1DE329129}" name="Entrada" dataDxfId="64"/>
+    <tableColumn id="4" xr3:uid="{B4D437CC-BE86-48EE-A5E0-DDF8C2D3FE46}" name="Salida Esperada" dataDxfId="63"/>
+    <tableColumn id="5" xr3:uid="{8F66F07B-9484-4B46-BFC9-4C1FA82FD510}" name="Salida Actual" dataDxfId="62"/>
+    <tableColumn id="6" xr3:uid="{A9ACCE28-457F-4CAB-928A-E811030162B9}" name="Resultados" dataDxfId="61"/>
+    <tableColumn id="7" xr3:uid="{8202AB49-3753-4B19-93DB-A214C9AEAA1E}" name="Comentarios" dataDxfId="60"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{F6EAB157-4A03-4734-A371-ECE98C5A8B56}" name="Table25678" displayName="Table25678" ref="A7:G16" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58" headerRowBorderDxfId="56" tableBorderDxfId="57" totalsRowBorderDxfId="55">
+  <autoFilter ref="A7:G16" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{79C4722B-D575-4C88-B14E-950993DDF4DF}" name="Numero de Paso" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{5CABB7B5-E9EA-44A3-B44C-A1D49A3330B1}" name="Accion" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{7E2ED526-6547-49AC-B2BF-B16B96875A42}" name="Entrada" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{591746D3-49B4-459B-9524-D4C90B410BCA}" name="Salida Esperada" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{F03F1792-672D-4C3D-A81F-13B7BAD2FEBA}" name="Salida Actual" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{8C7DD47F-352F-4358-8BBC-CA696825A03A}" name="Resultados" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{F485157E-4047-46AD-997E-E21FC50211FB}" name="Comentarios" dataDxfId="48"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0DE7532A-4DDC-43F2-8AC5-69A7E506824C}" name="Table256789" displayName="Table256789" ref="A7:G16" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34" headerRowBorderDxfId="32" tableBorderDxfId="33" totalsRowBorderDxfId="31">
+  <autoFilter ref="A7:G16" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{190CD8AC-04AE-4B2F-9CD5-7C7EE702DF30}" name="Numero de Paso" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{63925EC2-1DEA-4828-80E2-9EA6DF1B64CC}" name="Accion" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{7206C174-C076-43EB-A2D9-1FC5A7B02AEE}" name="Entrada" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{611A526B-18C9-485C-8AFC-95322D7C4E1F}" name="Salida Esperada" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{9DA77586-F2A4-481D-8973-D8B7E6A30728}" name="Salida Actual" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{E50AA112-5F53-4E9C-A44F-98C972706916}" name="Resultados" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{DD4A8BC7-98CB-445F-BB8E-9663AC0990B3}" name="Comentarios" dataDxfId="24"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{5AE7EA52-9370-44EA-B19F-A8D83949BE31}" name="Table210" displayName="Table210" ref="A7:G16" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" headerRowBorderDxfId="20" tableBorderDxfId="21" totalsRowBorderDxfId="19">
+  <autoFilter ref="A7:G16" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{24EA6C47-9D56-4508-89CA-F42764E02D4C}" name="Numero de Paso" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{35A859FE-EA69-4ED3-BFBB-69B4C2A3D8EA}" name="Accion" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{13B81CE2-4EDA-46B8-BD50-BD613668C846}" name="Entrada" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{D52A1946-1831-430B-B0AE-A197CEFB20F4}" name="Salida Esperada" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{DE5F89C9-5884-42F4-ABF2-C8CAA096BA8F}" name="Salida Actual" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{58290D2F-E10A-45A7-A8DF-2A7D48F7223B}" name="Resultados" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{7F085D3A-DC29-402F-AFB9-D194F0267EC8}" name="Comentarios" dataDxfId="12"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{4B93CADA-5029-4EA8-A8D6-C810E269AF0C}" name="Table21011" displayName="Table21011" ref="A7:G17" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+  <autoFilter ref="A7:G17" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{E74F4618-F641-4AAF-BEDD-0CF383F2B7D2}" name="Numero de Paso" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{A4D97019-799F-40A6-9BC5-7827B226D942}" name="Accion" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{393BB5D7-B1A6-4CD1-B39B-C9022B9F41F4}" name="Entrada" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{8E00BE9D-2515-43ED-A77D-35268F7265E3}" name="Salida Esperada" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{3B275CAF-A652-450A-9296-BF75053FC7D3}" name="Salida Actual" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{13211E02-C2B0-4E3A-83FC-A7B49BA559F9}" name="Resultados" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{93A359D5-8E27-4424-8730-2E15CC08E7AC}" name="Comentarios" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -989,7 +2680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC7464F8-FD2A-4AA0-91F8-5070CACB58B0}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" customWidth="1"/>
@@ -1002,299 +2693,279 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="30"/>
+      <c r="A1" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="28">
+        <v>1</v>
+      </c>
+      <c r="D2" s="29"/>
+      <c r="E2" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="26"/>
+    </row>
+    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="26"/>
+      <c r="E3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="26"/>
+    </row>
+    <row r="4" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="24">
-        <v>1</v>
-      </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="20"/>
-    </row>
-    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="20"/>
-    </row>
-    <row r="4" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="20"/>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="17"/>
+      <c r="A5" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="16"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="14"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="10" t="s">
+      <c r="A7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="B7" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>24</v>
       </c>
+      <c r="E7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8" s="8">
-        <v>1</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="5"/>
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="145" x14ac:dyDescent="0.35">
-      <c r="A9" s="8">
+      <c r="A9" s="7">
         <v>2</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="5"/>
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="8">
+      <c r="A10" s="7">
         <v>3</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="B10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" s="8">
+      <c r="D11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="8">
-        <v>5</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="8">
-        <v>6</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="1:7" ht="87" x14ac:dyDescent="0.35">
-      <c r="A14" s="8">
-        <v>7</v>
-      </c>
-      <c r="B14" s="7" t="s">
+      <c r="D15" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="7">
         <v>10</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="5"/>
-    </row>
-    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="8">
-        <v>8</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="8">
-        <v>9</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="5"/>
-    </row>
-    <row r="17" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="8">
-        <v>10</v>
-      </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="7" t="s">
+      <c r="C17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="5"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="8">
-        <v>11</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="4"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="1"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1315,4 +2986,2365 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67E29C34-DF65-45B8-AD19-1DFC37FA57BB}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" customWidth="1"/>
+    <col min="4" max="4" width="38.08984375" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="24"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="28">
+        <v>1</v>
+      </c>
+      <c r="D2" s="29"/>
+      <c r="E2" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="26"/>
+    </row>
+    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="26"/>
+      <c r="E3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="26"/>
+    </row>
+    <row r="4" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="26"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="203" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A5:G6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41B16007-58C5-48FC-8F60-85E556DEBCB4}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" customWidth="1"/>
+    <col min="4" max="4" width="38.08984375" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="24"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="28">
+        <v>1</v>
+      </c>
+      <c r="D2" s="29"/>
+      <c r="E2" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="26"/>
+    </row>
+    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="26"/>
+      <c r="E3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="26"/>
+    </row>
+    <row r="4" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="26"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="223.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A5:G6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADF569A5-AED4-47B8-8460-E603D5D489B6}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" customWidth="1"/>
+    <col min="4" max="4" width="38.08984375" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="24"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="28">
+        <v>1</v>
+      </c>
+      <c r="D2" s="29"/>
+      <c r="E2" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="26"/>
+    </row>
+    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="26"/>
+      <c r="E3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="26"/>
+    </row>
+    <row r="4" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="26"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="145" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A5:G6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D495AB40-047B-41EC-A79D-2B1889903331}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" customWidth="1"/>
+    <col min="4" max="4" width="38.08984375" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="24"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="28">
+        <v>1</v>
+      </c>
+      <c r="D2" s="29"/>
+      <c r="E2" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="26"/>
+    </row>
+    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="26"/>
+      <c r="E3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="26"/>
+    </row>
+    <row r="4" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="26"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="145" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A5:G6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ABA51BF-DCCA-410E-B01A-068343CED38D}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" customWidth="1"/>
+    <col min="4" max="4" width="38.08984375" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="24"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="28">
+        <v>1</v>
+      </c>
+      <c r="D2" s="29"/>
+      <c r="E2" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="26"/>
+    </row>
+    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="26"/>
+      <c r="E3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="26"/>
+    </row>
+    <row r="4" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="26"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="145" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A5:G6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4500079-5767-4667-A91F-52A8A3A10B11}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" customWidth="1"/>
+    <col min="4" max="4" width="38.08984375" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="24"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="28">
+        <v>1</v>
+      </c>
+      <c r="D2" s="29"/>
+      <c r="E2" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="26"/>
+    </row>
+    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="26"/>
+      <c r="E3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="26"/>
+    </row>
+    <row r="4" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="26"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="145" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A5:G6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7778A3F3-DDC3-4C3E-91B3-AA6F6F678769}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" customWidth="1"/>
+    <col min="4" max="4" width="38.08984375" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="24"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="28">
+        <v>1</v>
+      </c>
+      <c r="D2" s="29"/>
+      <c r="E2" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="26"/>
+    </row>
+    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="26"/>
+      <c r="E3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="26"/>
+    </row>
+    <row r="4" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="26"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="145" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A5:G6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED87AE3-3F4E-4B70-B5D9-D21301E9B529}">
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" customWidth="1"/>
+    <col min="4" max="4" width="38.08984375" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="24"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="28">
+        <v>1</v>
+      </c>
+      <c r="D2" s="29"/>
+      <c r="E2" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="26"/>
+    </row>
+    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="26"/>
+      <c r="E3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="26"/>
+    </row>
+    <row r="4" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="26"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="145" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="32">
+        <v>10</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A5:G6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/IngSoftware/propuesta/CasosDeTests/Casos de Test - Alta - Gestionar Producto.xlsx
+++ b/IngSoftware/propuesta/CasosDeTests/Casos de Test - Alta - Gestionar Producto.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\source\TrabajoFinalAus\IngSoftware\propuesta\CasosDeTests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DF30DB-079A-4709-B0E3-DD6EBBC42E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42EC614A-7441-4AE3-A9A5-2F9347B1601A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{907B4683-9A02-4D8C-B9E2-85A5E705A97A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{907B4683-9A02-4D8C-B9E2-85A5E705A97A}"/>
   </bookViews>
   <sheets>
-    <sheet name="1A-ALTA" sheetId="1" r:id="rId1"/>
-    <sheet name="1B-ALTA, SIN CATEGORIAS" sheetId="2" r:id="rId2"/>
-    <sheet name="1C-ALTA, SIN UNIDADES" sheetId="4" r:id="rId3"/>
-    <sheet name="1D-ALTA, ERROR NOMBRE" sheetId="7" r:id="rId4"/>
-    <sheet name="1E-ALTA ERROR DESCRIPCION" sheetId="12" r:id="rId5"/>
+    <sheet name="1A-CASO FELIZ" sheetId="1" r:id="rId1"/>
+    <sheet name="1B-SIN CATEGORIAS" sheetId="2" r:id="rId2"/>
+    <sheet name="1C-SIN UNIDADES" sheetId="4" r:id="rId3"/>
+    <sheet name="1D-ERROR NOMBRE" sheetId="7" r:id="rId4"/>
+    <sheet name="1E-ERROR DESCRIPCION" sheetId="12" r:id="rId5"/>
     <sheet name="1F-ERROR CANTIDAD" sheetId="13" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -279,26 +279,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -310,8 +298,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -439,29 +439,29 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -603,29 +603,29 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -647,6 +647,151 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -786,29 +931,48 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -931,29 +1095,29 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1095,29 +1259,29 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1136,170 +1300,6 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
@@ -1316,41 +1316,41 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6E43AC89-0E5C-4246-B8B3-33610FC8FE6B}" name="Table2" displayName="Table2" ref="A7:E9" totalsRowShown="0" headerRowDxfId="50" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57" totalsRowBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6E43AC89-0E5C-4246-B8B3-33610FC8FE6B}" name="Table2" displayName="Table2" ref="A7:E9" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="45">
   <autoFilter ref="A7:E9" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{24A6AD19-968B-4D0F-B19E-91A01420FF78}" name="Numero de Paso" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{D4259866-411E-40F1-898D-D467FD215EC2}" name="Accion" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{8129C9E6-1924-4286-A6C2-3EEBE58E3A1E}" name="Entrada" dataDxfId="53">
+    <tableColumn id="1" xr3:uid="{24A6AD19-968B-4D0F-B19E-91A01420FF78}" name="Numero de Paso" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{D4259866-411E-40F1-898D-D467FD215EC2}" name="Accion" dataDxfId="43"/>
+    <tableColumn id="8" xr3:uid="{8129C9E6-1924-4286-A6C2-3EEBE58E3A1E}" name="Entrada" dataDxfId="42">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0B1663DB-C235-4B08-86E1-8189BABE6031}" name="Resultados" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{CE6EDC0F-1D3F-474B-947A-9682A43024E4}" name="Comentarios" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{0B1663DB-C235-4B08-86E1-8189BABE6031}" name="Resultados" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{CE6EDC0F-1D3F-474B-947A-9682A43024E4}" name="Comentarios" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A69AFDA7-5333-4DFC-BE3B-ED11672B77E0}" name="Table23" displayName="Table23" ref="A7:E9" totalsRowShown="0" headerRowDxfId="49" dataDxfId="48" headerRowBorderDxfId="46" tableBorderDxfId="47" totalsRowBorderDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A69AFDA7-5333-4DFC-BE3B-ED11672B77E0}" name="Table23" displayName="Table23" ref="A7:E9" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
   <autoFilter ref="A7:E9" xr:uid="{A69AFDA7-5333-4DFC-BE3B-ED11672B77E0}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{56575A38-6385-4E32-959E-6FADA7A1B9DC}" name="Numero de Paso" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{0124314F-8F45-4DBF-865A-B9AFE3F427A5}" name="Accion" dataDxfId="43"/>
-    <tableColumn id="8" xr3:uid="{AD0A20D1-6635-486A-B087-CF3ADCB154A2}" name="Entrada" dataDxfId="42">
+    <tableColumn id="1" xr3:uid="{56575A38-6385-4E32-959E-6FADA7A1B9DC}" name="Numero de Paso" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{0124314F-8F45-4DBF-865A-B9AFE3F427A5}" name="Accion" dataDxfId="53"/>
+    <tableColumn id="8" xr3:uid="{AD0A20D1-6635-486A-B087-CF3ADCB154A2}" name="Entrada" dataDxfId="52">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{170FE1DC-9E41-476B-8831-18B106327E5A}" name="Resultados" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{4BDEDFFA-E9AA-47B7-AAB2-C58571DD752B}" name="Comentarios" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{170FE1DC-9E41-476B-8831-18B106327E5A}" name="Resultados" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{4BDEDFFA-E9AA-47B7-AAB2-C58571DD752B}" name="Comentarios" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C9423D3B-2AA7-4E84-BBB2-F3328569400B}" name="Table234" displayName="Table234" ref="A7:E9" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38" headerRowBorderDxfId="36" tableBorderDxfId="37" totalsRowBorderDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C9423D3B-2AA7-4E84-BBB2-F3328569400B}" name="Table234" displayName="Table234" ref="A7:E9" totalsRowShown="0" headerRowDxfId="39" dataDxfId="37" headerRowBorderDxfId="38" tableBorderDxfId="36" totalsRowBorderDxfId="35">
   <autoFilter ref="A7:E9" xr:uid="{C9423D3B-2AA7-4E84-BBB2-F3328569400B}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{56BB9DBC-E6D5-49A0-B2E9-694579D4C3FA}" name="Numero de Paso" dataDxfId="34"/>
@@ -1367,24 +1367,24 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4D7FFC4A-D03E-437C-ABEC-D1BEE1516B9E}" name="Table2345" displayName="Table2345" ref="A7:E9" totalsRowShown="0" headerRowDxfId="20" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28" totalsRowBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4D7FFC4A-D03E-437C-ABEC-D1BEE1516B9E}" name="Table2345" displayName="Table2345" ref="A7:E9" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="25">
   <autoFilter ref="A7:E9" xr:uid="{4D7FFC4A-D03E-437C-ABEC-D1BEE1516B9E}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9647289F-3F7D-4E9D-A95D-56095B2F12C5}" name="Numero de Paso" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{E589E827-D06E-4E49-96F2-C0B6031E5515}" name="Accion" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{63D171B5-892A-49D1-887F-844CDE9AE276}" name="Entrada" dataDxfId="23">
+    <tableColumn id="1" xr3:uid="{9647289F-3F7D-4E9D-A95D-56095B2F12C5}" name="Numero de Paso" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{E589E827-D06E-4E49-96F2-C0B6031E5515}" name="Accion" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{63D171B5-892A-49D1-887F-844CDE9AE276}" name="Entrada" dataDxfId="22">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5A27459D-3213-49DA-BF0F-EB708CC8FEE2}" name="Resultados" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{C759DDEF-3E5A-45DA-8FCC-843592A2910E}" name="Comentarios" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{5A27459D-3213-49DA-BF0F-EB708CC8FEE2}" name="Resultados" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{C759DDEF-3E5A-45DA-8FCC-843592A2910E}" name="Comentarios" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{70D06BD0-4AAC-42FB-B65A-C57E36ABD004}" name="Table23458" displayName="Table23458" ref="A7:E9" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{70D06BD0-4AAC-42FB-B65A-C57E36ABD004}" name="Table23458" displayName="Table23458" ref="A7:E9" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="A7:E9" xr:uid="{70D06BD0-4AAC-42FB-B65A-C57E36ABD004}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{B66041C0-EDAE-496F-977E-2AFE26696DC1}" name="Numero de Paso" dataDxfId="14"/>
@@ -1401,7 +1401,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{B6E49E3B-2594-4373-A9E8-31405D197DB6}" name="Table234589" displayName="Table234589" ref="A7:E9" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{B6E49E3B-2594-4373-A9E8-31405D197DB6}" name="Table234589" displayName="Table234589" ref="A7:E9" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="A7:E9" xr:uid="{B6E49E3B-2594-4373-A9E8-31405D197DB6}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{E3B76354-6614-4EC1-BB24-34C199C49138}" name="Numero de Paso" dataDxfId="4"/>
@@ -1745,94 +1745,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6">
+      <c r="B2" s="13"/>
+      <c r="C2" s="4">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="12"/>
+      <c r="C3" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="A8" s="10">
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1845,7 +1845,7 @@
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+      <c r="A9" s="10">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1887,108 +1887,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6">
+      <c r="B2" s="13"/>
+      <c r="C2" s="4">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
     </row>
     <row r="3" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="12"/>
+      <c r="C3" s="6" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="4" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" ht="90" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="A8" s="10">
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+      <c r="A9" s="10">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -2014,71 +2014,71 @@
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2108,94 +2108,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6">
+      <c r="B2" s="13"/>
+      <c r="C2" s="4">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="12"/>
+      <c r="C3" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="A8" s="10">
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -2208,7 +2208,7 @@
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+      <c r="A9" s="10">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -2247,94 +2247,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6">
+      <c r="B2" s="13"/>
+      <c r="C2" s="4">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="12"/>
+      <c r="C3" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="A8" s="10">
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -2347,7 +2347,7 @@
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+      <c r="A9" s="10">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -2386,94 +2386,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6">
+      <c r="B2" s="13"/>
+      <c r="C2" s="4">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="12"/>
+      <c r="C3" s="4" t="s">
         <v>34</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="A8" s="10">
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -2486,7 +2486,7 @@
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+      <c r="A9" s="10">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -2525,94 +2525,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6">
+      <c r="B2" s="13"/>
+      <c r="C2" s="4">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="12"/>
+      <c r="C3" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="A8" s="10">
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -2625,7 +2625,7 @@
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+      <c r="A9" s="10">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
